--- a/tables/ov_1_clean_test_ae_loss_metrics.xlsx
+++ b/tables/ov_1_clean_test_ae_loss_metrics.xlsx
@@ -419,19 +419,19 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Kennzahl</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Wert</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Rows</t>
+          <t>Zeilen</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -441,7 +441,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AE Threshold</t>
+          <t>AE-Schwelle</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mean Row MSE</t>
+          <t>Mittelwert Zeilen-MSE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -465,7 +465,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Std Row MSE</t>
+          <t>Std Zeilen-MSE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -477,7 +477,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Median Row MSE</t>
+          <t>Median Zeilen-MSE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -489,7 +489,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>95th Percentile Row MSE</t>
+          <t>95. Perzentil Zeilen-MSE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -501,7 +501,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Max Row MSE</t>
+          <t>Maximum Zeilen-MSE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
